--- a/data/trans_bre/P1418-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1418-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,74</t>
+          <t>7,9</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>67,84%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 9,65</t>
+          <t>3,94; 9,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,63; 13,26</t>
+          <t>7,95; 13,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,97; 11,8</t>
+          <t>6,21; 12,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,29; 10,92</t>
+          <t>4,46; 10,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,61; 99,28</t>
+          <t>30,81; 101,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,54; 199,44</t>
+          <t>85,48; 209,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,53; 223,53</t>
+          <t>82,74; 243,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28,8; 105,28</t>
+          <t>31,3; 108,97</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,59</t>
+          <t>3,01</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,98</t>
+          <t>1,16; 3,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,12</t>
+          <t>2,68; 5,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,01</t>
+          <t>1,79; 3,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,04</t>
+          <t>1,92; 4,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,54; 158,35</t>
+          <t>31,37; 160,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>159,96; 593,91</t>
+          <t>157,2; 619,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,32; 357,48</t>
+          <t>95,63; 347,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,11; 187,27</t>
+          <t>52,69; 159,75</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,87</t>
+          <t>3,1</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>167,22%</t>
+          <t>192,66%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 3,8</t>
+          <t>-0,71; 3,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 2,63</t>
+          <t>-0,87; 2,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 3,58</t>
+          <t>0,42; 3,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,97</t>
+          <t>1,61; 4,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,85; 240,62</t>
+          <t>-25,58; 231,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-56,59; 716,95</t>
+          <t>-69,87; 605,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 1624,72</t>
+          <t>-5,05; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46,49; 440,13</t>
+          <t>49,88; 498,75</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,26</t>
+          <t>4,6</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>106,3%</t>
+          <t>109,12%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 6,01</t>
+          <t>3,4; 5,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,45; 7,86</t>
+          <t>5,47; 7,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,68; 5,79</t>
+          <t>3,73; 5,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,63</t>
+          <t>3,59; 5,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>56,66; 125,54</t>
+          <t>56,74; 121,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>150,5; 296,73</t>
+          <t>151,97; 290,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>127,14; 271,07</t>
+          <t>129,78; 282,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>65,72; 167,75</t>
+          <t>75,13; 146,15</t>
         </is>
       </c>
     </row>
